--- a/price_target_vs_sp500_model_1.xlsx
+++ b/price_target_vs_sp500_model_1.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Claude_Code_workspaces\mehir-matara\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3896693-FFF4-4628-BED7-79F893248BC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B071DDC-DA5D-4EAF-97C4-39C7D568676D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="660" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="660" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="נתונים" sheetId="1" r:id="rId1"/>
-    <sheet name="לוח_סילוקין" sheetId="2" r:id="rId2"/>
-    <sheet name="השוואה_חודשית" sheetId="3" r:id="rId3"/>
-    <sheet name="דשבורד" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId2"/>
+    <sheet name="לוח_סילוקין" sheetId="2" r:id="rId3"/>
+    <sheet name="השוואה_חודשית" sheetId="3" r:id="rId4"/>
+    <sheet name="דשבורד" sheetId="4" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
@@ -1717,6 +1718,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E9608F0-77DE-4292-8553-1F6F202FCA6C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F361"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10750,7 +10760,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:R85"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -16952,7 +16962,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F24"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
